--- a/Data.xlsx
+++ b/Data.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert Wieringa\Documents\Studie\Civiele techniek\Master\Jaar 4\CIEM4120\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert Wieringa\Documents\Studie\Civiele techniek\Master\Jaar 4\CIEM4120\Offshore_Structures_Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE209315-5DE6-4BE0-98D1-A683922D1601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF72CE23-F25E-4EE7-AD10-8ECB79090CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{45F6CA14-2F83-475B-A8CB-BDBA7198FB4E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F028FC96-390B-4C76-B445-D230E46DA297}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Geometry" sheetId="1" r:id="rId1"/>
+    <sheet name="Members" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,36 +33,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={A395E05B-67FD-4F7F-A855-421B94E8BCB2}</author>
-  </authors>
-  <commentList>
-    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{C9D5D375-DB5F-4B40-AF46-CD3110684A04}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Always above
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="58">
   <si>
     <t>Nodes</t>
   </si>
@@ -78,46 +51,163 @@
     <t>Members</t>
   </si>
   <si>
-    <t>Nodes connected</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>2-5</t>
-  </si>
-  <si>
-    <t>6-5</t>
-  </si>
-  <si>
     <t>8-5</t>
   </si>
   <si>
-    <t>8-7</t>
-  </si>
-  <si>
     <t>8-9</t>
   </si>
   <si>
-    <t>10-9</t>
-  </si>
-  <si>
-    <t>1-12</t>
-  </si>
-  <si>
-    <t>3-11</t>
-  </si>
-  <si>
-    <t>Type of elem</t>
-  </si>
-  <si>
     <t>H</t>
   </si>
   <si>
     <t>K</t>
   </si>
   <si>
-    <t>Leg</t>
+    <t>20-17</t>
+  </si>
+  <si>
+    <t>Connectivity</t>
+  </si>
+  <si>
+    <t>Element type</t>
+  </si>
+  <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>7-8</t>
+  </si>
+  <si>
+    <t>5-10</t>
+  </si>
+  <si>
+    <t>6-10</t>
+  </si>
+  <si>
+    <t>9-10</t>
+  </si>
+  <si>
+    <t>6-11</t>
+  </si>
+  <si>
+    <t>7-12</t>
+  </si>
+  <si>
+    <t>10-11</t>
+  </si>
+  <si>
+    <t>11-12</t>
+  </si>
+  <si>
+    <t>12-9</t>
+  </si>
+  <si>
+    <t>10-13</t>
+  </si>
+  <si>
+    <t>10-14</t>
+  </si>
+  <si>
+    <t>11-14</t>
+  </si>
+  <si>
+    <t>12-15</t>
+  </si>
+  <si>
+    <t>9-16</t>
+  </si>
+  <si>
+    <t>13-14</t>
+  </si>
+  <si>
+    <t>14-15</t>
+  </si>
+  <si>
+    <t>15-16</t>
+  </si>
+  <si>
+    <t>16-13</t>
+  </si>
+  <si>
+    <t>13-18</t>
+  </si>
+  <si>
+    <t>14-19</t>
+  </si>
+  <si>
+    <t>15-20</t>
+  </si>
+  <si>
+    <t>16-17</t>
+  </si>
+  <si>
+    <t>17-18</t>
+  </si>
+  <si>
+    <t>18-19</t>
+  </si>
+  <si>
+    <t>19-20</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>5-9</t>
+  </si>
+  <si>
+    <t>9-13</t>
+  </si>
+  <si>
+    <t>13-17</t>
+  </si>
+  <si>
+    <t>17-21</t>
+  </si>
+  <si>
+    <t>2-6</t>
+  </si>
+  <si>
+    <t>14-18</t>
+  </si>
+  <si>
+    <t>18-22</t>
+  </si>
+  <si>
+    <t>3-7</t>
+  </si>
+  <si>
+    <t>7-11</t>
+  </si>
+  <si>
+    <t>11-15</t>
+  </si>
+  <si>
+    <t>15-19</t>
+  </si>
+  <si>
+    <t>19-23</t>
+  </si>
+  <si>
+    <t>4-8</t>
+  </si>
+  <si>
+    <t>8-12</t>
+  </si>
+  <si>
+    <t>12-16</t>
+  </si>
+  <si>
+    <t>16-20</t>
+  </si>
+  <si>
+    <t>20-24</t>
   </si>
 </sst>
 </file>
@@ -125,7 +215,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="172" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -156,18 +246,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -483,11 +576,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C84D05FA-50D8-46E7-8C2C-91FB0B0621E2}">
-  <dimension ref="A1:G13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7478CB75-A3D2-4026-B89E-C3DB5975153C}">
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="10.88671875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="8.88671875" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,275 +598,1019 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3">
+        <f>(25.53 + 1/10)/2</f>
+        <v>12.815000000000001</v>
+      </c>
+      <c r="C2" s="3">
+        <f>B2</f>
+        <v>12.815000000000001</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" s="3">
+        <f>B2</f>
+        <v>12.815000000000001</v>
+      </c>
+      <c r="C3" s="3">
+        <f>-C2</f>
+        <v>-12.815000000000001</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <f t="shared" ref="A4:A25" si="0">A3+1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <f>-B3</f>
+        <v>-12.815000000000001</v>
+      </c>
+      <c r="C4" s="3">
+        <f>C3</f>
+        <v>-12.815000000000001</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="B5" s="3">
+        <f>B4</f>
+        <v>-12.815000000000001</v>
+      </c>
+      <c r="C5" s="3">
+        <f>-C4</f>
+        <v>12.815000000000001</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="B6" s="5">
+        <f>(25.53)/2</f>
+        <v>12.765000000000001</v>
+      </c>
+      <c r="C6" s="5">
+        <f>B6</f>
+        <v>12.765000000000001</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="5">
+        <f>B6</f>
+        <v>12.765000000000001</v>
+      </c>
+      <c r="C7" s="5">
+        <f>-C6</f>
+        <v>-12.765000000000001</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="5">
+        <f>-B7</f>
+        <v>-12.765000000000001</v>
+      </c>
+      <c r="C8" s="5">
+        <f>C7</f>
+        <v>-12.765000000000001</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="5">
+        <f>B8</f>
+        <v>-12.765000000000001</v>
+      </c>
+      <c r="C9" s="5">
+        <f>-C8</f>
+        <v>12.765000000000001</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="5">
+        <f>(25.53/1.2523)/2</f>
+        <v>10.193244430248344</v>
+      </c>
+      <c r="C10" s="5">
+        <f>B10</f>
+        <v>10.193244430248344</v>
+      </c>
+      <c r="D10" s="2">
+        <f>D6+25.314</f>
+        <v>26.314</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="5">
+        <f>B10</f>
+        <v>10.193244430248344</v>
+      </c>
+      <c r="C11" s="5">
+        <f>-C10</f>
+        <v>-10.193244430248344</v>
+      </c>
+      <c r="D11" s="2">
+        <f>D7+25.314</f>
+        <v>26.314</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="5">
+        <f>-B11</f>
+        <v>-10.193244430248344</v>
+      </c>
+      <c r="C12" s="5">
+        <f>C11</f>
+        <v>-10.193244430248344</v>
+      </c>
+      <c r="D12" s="2">
+        <f>D8+25.314</f>
+        <v>26.314</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="5">
+        <f>B12</f>
+        <v>-10.193244430248344</v>
+      </c>
+      <c r="C13" s="5">
+        <f>-C12</f>
+        <v>10.193244430248344</v>
+      </c>
+      <c r="D13" s="2">
+        <f>D9+25.314</f>
+        <v>26.314</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="5">
+        <f>(20.213/1.2523)/2</f>
+        <v>8.0703505549788392</v>
+      </c>
+      <c r="C14" s="5">
+        <f>B14</f>
+        <v>8.0703505549788392</v>
+      </c>
+      <c r="D14" s="2">
+        <f>D10+20.213</f>
+        <v>46.527000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="5">
+        <f>B14</f>
+        <v>8.0703505549788392</v>
+      </c>
+      <c r="C15" s="5">
+        <f>-C14</f>
+        <v>-8.0703505549788392</v>
+      </c>
+      <c r="D15" s="2">
+        <f>D11+20.213</f>
+        <v>46.527000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="5">
+        <f>-B15</f>
+        <v>-8.0703505549788392</v>
+      </c>
+      <c r="C16" s="5">
+        <f>C15</f>
+        <v>-8.0703505549788392</v>
+      </c>
+      <c r="D16" s="2">
+        <f>D12+20.213</f>
+        <v>46.527000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="5">
+        <f>B16</f>
+        <v>-8.0703505549788392</v>
+      </c>
+      <c r="C17" s="5">
+        <f>-C16</f>
+        <v>8.0703505549788392</v>
+      </c>
+      <c r="D17" s="2">
+        <f>D13+20.213</f>
+        <v>46.527000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="5">
+        <f>(16.14/1.2523)/2</f>
+        <v>6.4441427772897875</v>
+      </c>
+      <c r="C18" s="5">
+        <f>B18</f>
+        <v>6.4441427772897875</v>
+      </c>
+      <c r="D18" s="2">
+        <f>D14+16.14</f>
+        <v>62.667000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="5">
+        <f>B18</f>
+        <v>6.4441427772897875</v>
+      </c>
+      <c r="C19" s="5">
+        <f>-C18</f>
+        <v>-6.4441427772897875</v>
+      </c>
+      <c r="D19" s="2">
+        <f>D15+16.14</f>
+        <v>62.667000000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="5">
+        <f>-B19</f>
+        <v>-6.4441427772897875</v>
+      </c>
+      <c r="C20" s="5">
+        <f>C19</f>
+        <v>-6.4441427772897875</v>
+      </c>
+      <c r="D20" s="2">
+        <f>D16+16.14</f>
+        <v>62.667000000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="5">
+        <f>B20</f>
+        <v>-6.4441427772897875</v>
+      </c>
+      <c r="C21" s="5">
+        <f>-C20</f>
+        <v>6.4441427772897875</v>
+      </c>
+      <c r="D21" s="2">
+        <f>D17+16.14</f>
+        <v>62.667000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B22" s="5">
+        <f>((16.14-1/10)/1.2523)/2</f>
+        <v>6.4042162421145088</v>
+      </c>
+      <c r="C22" s="5">
+        <f>B22</f>
+        <v>6.4042162421145088</v>
+      </c>
+      <c r="D22" s="2">
+        <f>D18+1</f>
+        <v>63.667000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B23" s="5">
+        <f>B22</f>
+        <v>6.4042162421145088</v>
+      </c>
+      <c r="C23" s="5">
+        <f>-C22</f>
+        <v>-6.4042162421145088</v>
+      </c>
+      <c r="D23" s="2">
+        <f>D19+1</f>
+        <v>63.667000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B24" s="5">
+        <f>-B23</f>
+        <v>-6.4042162421145088</v>
+      </c>
+      <c r="C24" s="5">
+        <f>C23</f>
+        <v>-6.4042162421145088</v>
+      </c>
+      <c r="D24" s="2">
+        <f>D20+1</f>
+        <v>63.667000000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B25" s="5">
+        <f>B24</f>
+        <v>-6.4042162421145088</v>
+      </c>
+      <c r="C25" s="5">
+        <f>-C24</f>
+        <v>6.4042162421145088</v>
+      </c>
+      <c r="D25" s="2">
+        <f>D21+1</f>
+        <v>63.667000000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" ht="39" customHeight="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE55AB2D-FD9C-4239-9973-5E0FF7067271}">
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="15.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.21875" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <f t="shared" ref="A4:A10" si="0">A3+1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3">
-        <v>2</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2">
-        <v>25.53</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3">
-        <v>3</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="C22" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f>A25+1</f>
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" ref="A27:A33" si="1">A26+1</f>
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" ref="A34:A49" si="2">A33+1</f>
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2">
-        <v>25.530519647835497</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3">
-        <v>4</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2">
-        <v>22.958659384999997</v>
-      </c>
-      <c r="C6" s="2">
-        <v>26.314</v>
-      </c>
-      <c r="D6" s="1">
-        <f>1+16.14</f>
-        <v>17.14</v>
-      </c>
-      <c r="E6" s="3">
-        <v>5</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2">
-        <v>2.5713406150000022</v>
-      </c>
-      <c r="C7" s="2">
-        <v>26.314</v>
-      </c>
-      <c r="D7" s="1">
-        <f>D6</f>
-        <v>17.14</v>
-      </c>
-      <c r="E7" s="3">
-        <v>6</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2">
-        <v>20.904949999999999</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46.527000000000001</v>
-      </c>
-      <c r="D8" s="1">
-        <f>D7+20.213</f>
-        <v>37.353000000000002</v>
-      </c>
-      <c r="E8" s="3">
-        <v>7</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2">
-        <v>4.6250500000000017</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46.527000000000001</v>
-      </c>
-      <c r="D9" s="1">
-        <f>D8</f>
-        <v>37.353000000000002</v>
-      </c>
-      <c r="E9" s="3">
-        <v>8</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2">
-        <v>19.265000000000001</v>
-      </c>
-      <c r="C10" s="2">
-        <v>62.667000000000002</v>
-      </c>
-      <c r="D10" s="1">
-        <f>D9+25.314</f>
-        <v>62.667000000000002</v>
-      </c>
-      <c r="E10" s="3">
-        <v>9</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2">
-        <v>6.2650000000000006</v>
-      </c>
-      <c r="C11" s="2">
-        <v>62.667000000000002</v>
-      </c>
-      <c r="D11" s="1">
-        <f>D10</f>
-        <v>62.667000000000002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2">
-        <v>19.164999999999999</v>
-      </c>
-      <c r="C12" s="2">
-        <v>63.667000000000002</v>
-      </c>
-      <c r="D12" s="1">
-        <f>D11+1</f>
-        <v>63.667000000000002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2">
-        <v>6.3650000000000002</v>
-      </c>
-      <c r="C13" s="2">
-        <v>63.667000000000002</v>
-      </c>
-      <c r="D13" s="1">
-        <f>D12</f>
-        <v>63.667000000000002</v>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="2"/>
+        <v>37</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="2"/>
+        <v>38</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="2"/>
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>